--- a/final_data_pipeline/output/325312_elec_options.xlsx
+++ b/final_data_pipeline/output/325312_elec_options.xlsx
@@ -828,7 +828,7 @@
         <v>84</v>
       </c>
       <c r="AD2">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE2">
         <v>8000</v>
@@ -923,7 +923,7 @@
         <v>84</v>
       </c>
       <c r="AD3">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE3">
         <v>8000</v>
@@ -2372,7 +2372,7 @@
         <v>84</v>
       </c>
       <c r="AD18">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE18">
         <v>8000</v>
@@ -2467,7 +2467,7 @@
         <v>84</v>
       </c>
       <c r="AD19">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE19">
         <v>8000</v>
@@ -4495,7 +4495,7 @@
         <v>84</v>
       </c>
       <c r="AD40">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE40">
         <v>8000</v>
@@ -4593,7 +4593,7 @@
         <v>84</v>
       </c>
       <c r="AD41">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE41">
         <v>8000</v>
@@ -4688,7 +4688,7 @@
         <v>84</v>
       </c>
       <c r="AD42">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE42">
         <v>8000</v>
@@ -4783,7 +4783,7 @@
         <v>84</v>
       </c>
       <c r="AD43">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE43">
         <v>8000</v>
@@ -4881,7 +4881,7 @@
         <v>84</v>
       </c>
       <c r="AD44">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE44">
         <v>8000</v>
@@ -4979,7 +4979,7 @@
         <v>84</v>
       </c>
       <c r="AD45">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE45">
         <v>8000</v>
@@ -5074,7 +5074,7 @@
         <v>84</v>
       </c>
       <c r="AD46">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE46">
         <v>8000</v>
@@ -5169,7 +5169,7 @@
         <v>84</v>
       </c>
       <c r="AD47">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AE47">
         <v>8000</v>
